--- a/htr-update-fr-medication/ig/StructureDefinition-fr-family-member-history-body-site-extension.xlsx
+++ b/htr-update-fr-medication/ig/StructureDefinition-fr-family-member-history-body-site-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T08:28:14+00:00</t>
+    <t>2026-09-04T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
